--- a/education_surveys/022_dormitory_preference_survey--education_surveys.xlsx
+++ b/education_surveys/022_dormitory_preference_survey--education_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -983,12 +983,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1016,12 +1016,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'private_room',_'label':_'private_room'}</t>
+          <t>private_room</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Private Room', 'label': 'Private Room'}</t>
+          <t>Private Room</t>
         </is>
       </c>
     </row>
@@ -1033,12 +1033,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'shared_room',_'label':_'shared_room'}</t>
+          <t>shared_room</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Shared Room', 'label': 'Shared Room'}</t>
+          <t>Shared Room</t>
         </is>
       </c>
     </row>
@@ -1050,12 +1050,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'male',_'label':_'male'}</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Male', 'label': 'Male'}</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'female',_'label':_'female'}</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Female', 'label': 'Female'}</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -1084,12 +1084,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'non-binary',_'label':_'non-binary'}</t>
+          <t>non-binary</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Non-Binary', 'label': 'Non-Binary'}</t>
+          <t>Non-Binary</t>
         </is>
       </c>
     </row>
@@ -1101,12 +1101,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'english',_'label':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'English', 'label': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1118,12 +1118,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'mandarin',_'label':_'mandarin'}</t>
+          <t>mandarin</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Mandarin', 'label': 'Mandarin'}</t>
+          <t>Mandarin</t>
         </is>
       </c>
     </row>
@@ -1135,12 +1135,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'spanish',_'label':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Spanish', 'label': 'Spanish'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'omnivore',_'label':_'omnivore'}</t>
+          <t>omnivore</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Omnivore', 'label': 'Omnivore'}</t>
+          <t>Omnivore</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'vegetarian',_'label':_'vegetarian'}</t>
+          <t>vegetarian</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Vegetarian', 'label': 'Vegetarian'}</t>
+          <t>Vegetarian</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'vegan',_'label':_'vegan'}</t>
+          <t>vegan</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Vegan', 'label': 'Vegan'}</t>
+          <t>Vegan</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'air_conditioning',_'label':_'air_conditioning'}</t>
+          <t>air_conditioning</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Air Conditioning', 'label': 'Air Conditioning'}</t>
+          <t>Air Conditioning</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'balcony',_'label':_'balcony'}</t>
+          <t>balcony</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Balcony', 'label': 'Balcony'}</t>
+          <t>Balcony</t>
         </is>
       </c>
     </row>
@@ -1237,12 +1237,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'balcony',_'label':_'balcony'}</t>
+          <t>microwave</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Balcony', 'label': 'Balcony'}</t>
+          <t>Microwave</t>
         </is>
       </c>
     </row>
@@ -1254,29 +1254,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'microwave',_'label':_'microwave'}</t>
+          <t>tv</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Microwave', 'label': 'Microwave'}</t>
+          <t>TV</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>amenities_choices</t>
+          <t>floor_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'tv',_'label':_'tv'}</t>
+          <t>ground_floor</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'TV', 'label': 'TV'}</t>
+          <t>Ground Floor</t>
         </is>
       </c>
     </row>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'ground',_'label':_'ground_floor'}</t>
+          <t>first_floor</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Ground', 'label': 'Ground Floor'}</t>
+          <t>First Floor</t>
         </is>
       </c>
     </row>
@@ -1305,12 +1305,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'first',_'label':_'first_floor'}</t>
+          <t>second_floor</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'First', 'label': 'First Floor'}</t>
+          <t>Second Floor</t>
         </is>
       </c>
     </row>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'second',_'label':_'second_floor'}</t>
+          <t>third_floor</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'Second', 'label': 'Second Floor'}</t>
+          <t>Third Floor</t>
         </is>
       </c>
     </row>
@@ -1339,29 +1339,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'third',_'label':_'third_floor'}</t>
+          <t>fourth_floor</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'Third', 'label': 'Third Floor'}</t>
+          <t>Fourth Floor</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>floor_choices</t>
+          <t>room_orientation_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'fourth',_'label':_'fourth_floor'}</t>
+          <t>north</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'Fourth', 'label': 'Fourth Floor'}</t>
+          <t>North</t>
         </is>
       </c>
     </row>
@@ -1373,12 +1373,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'north',_'label':_'north'}</t>
+          <t>south</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'North', 'label': 'North'}</t>
+          <t>South</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'south',_'label':_'south'}</t>
+          <t>east</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'South', 'label': 'South'}</t>
+          <t>East</t>
         </is>
       </c>
     </row>
@@ -1407,29 +1407,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'east',_'label':_'east'}</t>
+          <t>west</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'East', 'label': 'East'}</t>
+          <t>West</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>room_orientation_choices</t>
+          <t>accessibility_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_'west',_'label':_'west'}</t>
+          <t>wheelchair</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 'West', 'label': 'West'}</t>
+          <t>Wheelchair</t>
         </is>
       </c>
     </row>
@@ -1441,12 +1441,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_'wheelchair',_'label':_'wheelchair'}</t>
+          <t>hearing</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 'Wheelchair', 'label': 'Wheelchair'}</t>
+          <t>Hearing</t>
         </is>
       </c>
     </row>
@@ -1458,12 +1458,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_'hearing',_'label':_'hearing'}</t>
+          <t>blindness</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': 'Hearing', 'label': 'Hearing'}</t>
+          <t>Blindness</t>
         </is>
       </c>
     </row>
@@ -1475,29 +1475,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'value':_'blindness',_'label':_'blindness'}</t>
+          <t>vision</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'value': 'Blindness', 'label': 'Blindness'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>accessibility_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>{'value':_'vision',_'label':_'vision'}</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>{'value': 'Vision', 'label': 'Vision'}</t>
+          <t>Vision</t>
         </is>
       </c>
     </row>
